--- a/public/data/data-airminum.xlsx
+++ b/public/data/data-airminum.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\airminum-dashboard\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241598DA-AA03-4554-9EE0-2154CDB6821D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71167C5C-B727-4E21-AFE7-94394A9522AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{637E1199-51FA-4416-80B8-A59217F71B89}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{637E1199-51FA-4416-80B8-A59217F71B89}"/>
   </bookViews>
   <sheets>
-    <sheet name="akses_nas" sheetId="1" r:id="rId1"/>
+    <sheet name="akses" sheetId="1" r:id="rId1"/>
+    <sheet name="infrastruktur" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="81">
   <si>
     <t>kode_wilayah</t>
   </si>
@@ -207,6 +208,81 @@
   </si>
   <si>
     <t>provinsi</t>
+  </si>
+  <si>
+    <t>nilai</t>
+  </si>
+  <si>
+    <t>NRW Produksi</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>IPA</t>
+  </si>
+  <si>
+    <t>KEB</t>
+  </si>
+  <si>
+    <t>ABIC</t>
+  </si>
+  <si>
+    <t>IPAX</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PRODIC</t>
+  </si>
+  <si>
+    <t>PRODRIIL</t>
+  </si>
+  <si>
+    <t>PRODX</t>
+  </si>
+  <si>
+    <t>DIS</t>
+  </si>
+  <si>
+    <t>DISX</t>
+  </si>
+  <si>
+    <t>JUAL</t>
+  </si>
+  <si>
+    <t>liter/detik</t>
+  </si>
+  <si>
+    <t>Air Baku</t>
+  </si>
+  <si>
+    <t>Kebutuhan</t>
+  </si>
+  <si>
+    <t>AB Idle</t>
+  </si>
+  <si>
+    <t>IPA Rusak</t>
+  </si>
+  <si>
+    <t>Kap. Produksi</t>
+  </si>
+  <si>
+    <t>IPA Idle</t>
+  </si>
+  <si>
+    <t>Produksi Riil</t>
+  </si>
+  <si>
+    <t>Vol. Distribusi</t>
+  </si>
+  <si>
+    <t>NRW Distribusi</t>
+  </si>
+  <si>
+    <t>Vol. Terjual</t>
   </si>
 </sst>
 </file>
@@ -250,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -258,7 +334,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1060,7 +1135,7 @@
       <c r="E14" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>11</v>
       </c>
       <c r="G14">
@@ -1089,7 +1164,7 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15">
         <v>12</v>
       </c>
       <c r="G15">
@@ -1118,7 +1193,7 @@
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16">
         <v>13</v>
       </c>
       <c r="G16">
@@ -1147,7 +1222,7 @@
       <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>14</v>
       </c>
       <c r="G17">
@@ -1176,7 +1251,7 @@
       <c r="E18" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18">
         <v>15</v>
       </c>
       <c r="G18">
@@ -1205,7 +1280,7 @@
       <c r="E19" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>16</v>
       </c>
       <c r="G19">
@@ -1234,7 +1309,7 @@
       <c r="E20" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20">
         <v>17</v>
       </c>
       <c r="G20">
@@ -1263,7 +1338,7 @@
       <c r="E21" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>18</v>
       </c>
       <c r="G21">
@@ -1292,7 +1367,7 @@
       <c r="E22" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22">
         <v>19</v>
       </c>
       <c r="G22">
@@ -1321,7 +1396,7 @@
       <c r="E23" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23">
         <v>21</v>
       </c>
       <c r="G23">
@@ -1350,7 +1425,7 @@
       <c r="E24" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>31</v>
       </c>
       <c r="G24">
@@ -1379,7 +1454,7 @@
       <c r="E25" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>32</v>
       </c>
       <c r="G25">
@@ -1408,7 +1483,7 @@
       <c r="E26" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26">
         <v>33</v>
       </c>
       <c r="G26">
@@ -1437,7 +1512,7 @@
       <c r="E27" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27">
         <v>34</v>
       </c>
       <c r="G27">
@@ -1466,7 +1541,7 @@
       <c r="E28" t="s">
         <v>31</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28">
         <v>35</v>
       </c>
       <c r="G28">
@@ -1495,7 +1570,7 @@
       <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29">
         <v>36</v>
       </c>
       <c r="G29">
@@ -1524,7 +1599,7 @@
       <c r="E30" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30">
         <v>51</v>
       </c>
       <c r="G30">
@@ -1553,7 +1628,7 @@
       <c r="E31" t="s">
         <v>34</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31">
         <v>52</v>
       </c>
       <c r="G31">
@@ -1582,7 +1657,7 @@
       <c r="E32" t="s">
         <v>35</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32">
         <v>53</v>
       </c>
       <c r="G32">
@@ -1611,7 +1686,7 @@
       <c r="E33" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33">
         <v>61</v>
       </c>
       <c r="G33">
@@ -1640,7 +1715,7 @@
       <c r="E34" t="s">
         <v>37</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34">
         <v>62</v>
       </c>
       <c r="G34">
@@ -1669,7 +1744,7 @@
       <c r="E35" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35">
         <v>63</v>
       </c>
       <c r="G35">
@@ -1698,7 +1773,7 @@
       <c r="E36" t="s">
         <v>39</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36">
         <v>64</v>
       </c>
       <c r="G36">
@@ -1727,7 +1802,7 @@
       <c r="E37" t="s">
         <v>40</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37">
         <v>65</v>
       </c>
       <c r="G37">
@@ -1756,7 +1831,7 @@
       <c r="E38" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38">
         <v>71</v>
       </c>
       <c r="G38">
@@ -1785,7 +1860,7 @@
       <c r="E39" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39">
         <v>72</v>
       </c>
       <c r="G39">
@@ -1814,7 +1889,7 @@
       <c r="E40" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40">
         <v>73</v>
       </c>
       <c r="G40">
@@ -1843,7 +1918,7 @@
       <c r="E41" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41">
         <v>74</v>
       </c>
       <c r="G41">
@@ -1872,7 +1947,7 @@
       <c r="E42" t="s">
         <v>45</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42">
         <v>75</v>
       </c>
       <c r="G42">
@@ -1901,7 +1976,7 @@
       <c r="E43" t="s">
         <v>46</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43">
         <v>76</v>
       </c>
       <c r="G43">
@@ -1930,7 +2005,7 @@
       <c r="E44" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44">
         <v>81</v>
       </c>
       <c r="G44">
@@ -1959,7 +2034,7 @@
       <c r="E45" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45">
         <v>82</v>
       </c>
       <c r="G45">
@@ -1988,7 +2063,7 @@
       <c r="E46" t="s">
         <v>49</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46">
         <v>91</v>
       </c>
       <c r="G46">
@@ -2017,7 +2092,7 @@
       <c r="E47" t="s">
         <v>50</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47">
         <v>94</v>
       </c>
       <c r="G47">
@@ -2046,7 +2121,7 @@
       <c r="E48" t="s">
         <v>51</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48">
         <v>95</v>
       </c>
       <c r="G48">
@@ -2075,7 +2150,7 @@
       <c r="E49" t="s">
         <v>52</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49">
         <v>96</v>
       </c>
       <c r="G49">
@@ -2101,7 +2176,7 @@
       <c r="E50" t="s">
         <v>53</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50">
         <v>97</v>
       </c>
       <c r="G50">
@@ -2127,7 +2202,7 @@
       <c r="E51" t="s">
         <v>54</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51">
         <v>98</v>
       </c>
       <c r="G51">
@@ -2156,7 +2231,7 @@
       <c r="E52" t="s">
         <v>17</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52">
         <v>11</v>
       </c>
       <c r="G52">
@@ -2185,7 +2260,7 @@
       <c r="E53" t="s">
         <v>18</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53">
         <v>12</v>
       </c>
       <c r="G53">
@@ -2214,7 +2289,7 @@
       <c r="E54" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54">
         <v>13</v>
       </c>
       <c r="G54">
@@ -2243,7 +2318,7 @@
       <c r="E55" t="s">
         <v>20</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55">
         <v>14</v>
       </c>
       <c r="G55">
@@ -2272,7 +2347,7 @@
       <c r="E56" t="s">
         <v>21</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56">
         <v>15</v>
       </c>
       <c r="G56">
@@ -2301,7 +2376,7 @@
       <c r="E57" t="s">
         <v>22</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57">
         <v>16</v>
       </c>
       <c r="G57">
@@ -2330,7 +2405,7 @@
       <c r="E58" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58">
         <v>17</v>
       </c>
       <c r="G58">
@@ -2359,7 +2434,7 @@
       <c r="E59" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59">
         <v>18</v>
       </c>
       <c r="G59">
@@ -2388,7 +2463,7 @@
       <c r="E60" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60">
         <v>19</v>
       </c>
       <c r="G60">
@@ -2417,7 +2492,7 @@
       <c r="E61" t="s">
         <v>26</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61">
         <v>21</v>
       </c>
       <c r="G61">
@@ -2446,7 +2521,7 @@
       <c r="E62" t="s">
         <v>27</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62">
         <v>31</v>
       </c>
       <c r="G62">
@@ -2475,7 +2550,7 @@
       <c r="E63" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63">
         <v>32</v>
       </c>
       <c r="G63">
@@ -2504,7 +2579,7 @@
       <c r="E64" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64">
         <v>33</v>
       </c>
       <c r="G64">
@@ -2533,7 +2608,7 @@
       <c r="E65" t="s">
         <v>30</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65">
         <v>34</v>
       </c>
       <c r="G65">
@@ -2562,7 +2637,7 @@
       <c r="E66" t="s">
         <v>31</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66">
         <v>35</v>
       </c>
       <c r="G66">
@@ -2591,7 +2666,7 @@
       <c r="E67" t="s">
         <v>32</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67">
         <v>36</v>
       </c>
       <c r="G67">
@@ -2620,7 +2695,7 @@
       <c r="E68" t="s">
         <v>33</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68">
         <v>51</v>
       </c>
       <c r="G68">
@@ -2649,7 +2724,7 @@
       <c r="E69" t="s">
         <v>34</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>52</v>
       </c>
       <c r="G69">
@@ -2678,7 +2753,7 @@
       <c r="E70" t="s">
         <v>35</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70">
         <v>53</v>
       </c>
       <c r="G70">
@@ -2707,7 +2782,7 @@
       <c r="E71" t="s">
         <v>36</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71">
         <v>61</v>
       </c>
       <c r="G71">
@@ -2736,7 +2811,7 @@
       <c r="E72" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72">
         <v>62</v>
       </c>
       <c r="G72">
@@ -2765,7 +2840,7 @@
       <c r="E73" t="s">
         <v>38</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73">
         <v>63</v>
       </c>
       <c r="G73">
@@ -2794,7 +2869,7 @@
       <c r="E74" t="s">
         <v>39</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74">
         <v>64</v>
       </c>
       <c r="G74">
@@ -2823,7 +2898,7 @@
       <c r="E75" t="s">
         <v>40</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75">
         <v>65</v>
       </c>
       <c r="G75">
@@ -2852,7 +2927,7 @@
       <c r="E76" t="s">
         <v>41</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76">
         <v>71</v>
       </c>
       <c r="G76">
@@ -2881,7 +2956,7 @@
       <c r="E77" t="s">
         <v>42</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77">
         <v>72</v>
       </c>
       <c r="G77">
@@ -2910,7 +2985,7 @@
       <c r="E78" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78">
         <v>73</v>
       </c>
       <c r="G78">
@@ -2939,7 +3014,7 @@
       <c r="E79" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79">
         <v>74</v>
       </c>
       <c r="G79">
@@ -2968,7 +3043,7 @@
       <c r="E80" t="s">
         <v>45</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80">
         <v>75</v>
       </c>
       <c r="G80">
@@ -2997,7 +3072,7 @@
       <c r="E81" t="s">
         <v>46</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81">
         <v>76</v>
       </c>
       <c r="G81">
@@ -3026,7 +3101,7 @@
       <c r="E82" t="s">
         <v>47</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82">
         <v>81</v>
       </c>
       <c r="G82">
@@ -3055,7 +3130,7 @@
       <c r="E83" t="s">
         <v>48</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83">
         <v>82</v>
       </c>
       <c r="G83">
@@ -3084,7 +3159,7 @@
       <c r="E84" t="s">
         <v>49</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84">
         <v>91</v>
       </c>
       <c r="G84">
@@ -3113,7 +3188,7 @@
       <c r="E85" t="s">
         <v>50</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85">
         <v>94</v>
       </c>
       <c r="G85">
@@ -3142,7 +3217,7 @@
       <c r="E86" t="s">
         <v>51</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86">
         <v>95</v>
       </c>
       <c r="G86">
@@ -3171,7 +3246,7 @@
       <c r="E87" t="s">
         <v>52</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87">
         <v>96</v>
       </c>
       <c r="G87">
@@ -3200,7 +3275,7 @@
       <c r="E88" t="s">
         <v>53</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88">
         <v>97</v>
       </c>
       <c r="G88">
@@ -3229,7 +3304,7 @@
       <c r="E89" t="s">
         <v>54</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89">
         <v>98</v>
       </c>
       <c r="G89">
@@ -3258,7 +3333,7 @@
       <c r="E90" t="s">
         <v>17</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90">
         <v>11</v>
       </c>
       <c r="G90">
@@ -3284,7 +3359,7 @@
       <c r="E91" t="s">
         <v>18</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91">
         <v>12</v>
       </c>
       <c r="G91">
@@ -3310,7 +3385,7 @@
       <c r="E92" t="s">
         <v>19</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92">
         <v>13</v>
       </c>
       <c r="G92">
@@ -3336,7 +3411,7 @@
       <c r="E93" t="s">
         <v>20</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93">
         <v>14</v>
       </c>
       <c r="G93">
@@ -3362,7 +3437,7 @@
       <c r="E94" t="s">
         <v>21</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94">
         <v>15</v>
       </c>
       <c r="G94">
@@ -3388,7 +3463,7 @@
       <c r="E95" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95">
         <v>16</v>
       </c>
       <c r="G95">
@@ -3414,7 +3489,7 @@
       <c r="E96" t="s">
         <v>23</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96">
         <v>17</v>
       </c>
       <c r="G96">
@@ -3440,7 +3515,7 @@
       <c r="E97" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97">
         <v>18</v>
       </c>
       <c r="G97">
@@ -3466,7 +3541,7 @@
       <c r="E98" t="s">
         <v>25</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98">
         <v>19</v>
       </c>
       <c r="G98">
@@ -3492,7 +3567,7 @@
       <c r="E99" t="s">
         <v>26</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99">
         <v>21</v>
       </c>
       <c r="G99">
@@ -3518,7 +3593,7 @@
       <c r="E100" t="s">
         <v>27</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100">
         <v>31</v>
       </c>
       <c r="G100">
@@ -3544,7 +3619,7 @@
       <c r="E101" t="s">
         <v>28</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101">
         <v>32</v>
       </c>
       <c r="G101">
@@ -3570,7 +3645,7 @@
       <c r="E102" t="s">
         <v>29</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102">
         <v>33</v>
       </c>
       <c r="G102">
@@ -3596,7 +3671,7 @@
       <c r="E103" t="s">
         <v>30</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103">
         <v>34</v>
       </c>
       <c r="G103">
@@ -3622,7 +3697,7 @@
       <c r="E104" t="s">
         <v>31</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104">
         <v>35</v>
       </c>
       <c r="G104">
@@ -3648,7 +3723,7 @@
       <c r="E105" t="s">
         <v>32</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105">
         <v>36</v>
       </c>
       <c r="G105">
@@ -3674,7 +3749,7 @@
       <c r="E106" t="s">
         <v>33</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106">
         <v>51</v>
       </c>
       <c r="G106">
@@ -3700,7 +3775,7 @@
       <c r="E107" t="s">
         <v>34</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107">
         <v>52</v>
       </c>
       <c r="G107">
@@ -3726,7 +3801,7 @@
       <c r="E108" t="s">
         <v>35</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108">
         <v>53</v>
       </c>
       <c r="G108">
@@ -3752,7 +3827,7 @@
       <c r="E109" t="s">
         <v>36</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109">
         <v>61</v>
       </c>
       <c r="G109">
@@ -3778,7 +3853,7 @@
       <c r="E110" t="s">
         <v>37</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110">
         <v>62</v>
       </c>
       <c r="G110">
@@ -3804,7 +3879,7 @@
       <c r="E111" t="s">
         <v>38</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111">
         <v>63</v>
       </c>
       <c r="G111">
@@ -3830,7 +3905,7 @@
       <c r="E112" t="s">
         <v>39</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112">
         <v>64</v>
       </c>
       <c r="G112">
@@ -3856,7 +3931,7 @@
       <c r="E113" t="s">
         <v>40</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113">
         <v>65</v>
       </c>
       <c r="G113">
@@ -3882,7 +3957,7 @@
       <c r="E114" t="s">
         <v>41</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114">
         <v>71</v>
       </c>
       <c r="G114">
@@ -3908,7 +3983,7 @@
       <c r="E115" t="s">
         <v>42</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115">
         <v>72</v>
       </c>
       <c r="G115">
@@ -3934,7 +4009,7 @@
       <c r="E116" t="s">
         <v>43</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116">
         <v>73</v>
       </c>
       <c r="G116">
@@ -3960,7 +4035,7 @@
       <c r="E117" t="s">
         <v>44</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117">
         <v>74</v>
       </c>
       <c r="G117">
@@ -3986,7 +4061,7 @@
       <c r="E118" t="s">
         <v>45</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118">
         <v>75</v>
       </c>
       <c r="G118">
@@ -4012,7 +4087,7 @@
       <c r="E119" t="s">
         <v>46</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119">
         <v>76</v>
       </c>
       <c r="G119">
@@ -4038,7 +4113,7 @@
       <c r="E120" t="s">
         <v>47</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120">
         <v>81</v>
       </c>
       <c r="G120">
@@ -4064,7 +4139,7 @@
       <c r="E121" t="s">
         <v>48</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121">
         <v>82</v>
       </c>
       <c r="G121">
@@ -4090,7 +4165,7 @@
       <c r="E122" t="s">
         <v>49</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122">
         <v>91</v>
       </c>
       <c r="G122">
@@ -4116,7 +4191,7 @@
       <c r="E123" t="s">
         <v>50</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123">
         <v>94</v>
       </c>
       <c r="G123">
@@ -4142,7 +4217,7 @@
       <c r="E124" t="s">
         <v>51</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124">
         <v>95</v>
       </c>
       <c r="G124">
@@ -4168,7 +4243,7 @@
       <c r="E125" t="s">
         <v>52</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125">
         <v>96</v>
       </c>
       <c r="G125">
@@ -4194,7 +4269,7 @@
       <c r="E126" t="s">
         <v>53</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126">
         <v>97</v>
       </c>
       <c r="G126">
@@ -4220,7 +4295,7 @@
       <c r="E127" t="s">
         <v>54</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127">
         <v>98</v>
       </c>
       <c r="G127">
@@ -4246,7 +4321,7 @@
       <c r="E128" t="s">
         <v>17</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128">
         <v>11</v>
       </c>
       <c r="G128">
@@ -4275,7 +4350,7 @@
       <c r="E129" t="s">
         <v>18</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129">
         <v>12</v>
       </c>
       <c r="G129">
@@ -4304,7 +4379,7 @@
       <c r="E130" t="s">
         <v>19</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130">
         <v>13</v>
       </c>
       <c r="G130">
@@ -4333,7 +4408,7 @@
       <c r="E131" t="s">
         <v>20</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131">
         <v>14</v>
       </c>
       <c r="G131">
@@ -4362,7 +4437,7 @@
       <c r="E132" t="s">
         <v>21</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132">
         <v>15</v>
       </c>
       <c r="G132">
@@ -4391,7 +4466,7 @@
       <c r="E133" t="s">
         <v>22</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133">
         <v>16</v>
       </c>
       <c r="G133">
@@ -4420,7 +4495,7 @@
       <c r="E134" t="s">
         <v>23</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134">
         <v>17</v>
       </c>
       <c r="G134">
@@ -4449,7 +4524,7 @@
       <c r="E135" t="s">
         <v>24</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135">
         <v>18</v>
       </c>
       <c r="G135">
@@ -4478,7 +4553,7 @@
       <c r="E136" t="s">
         <v>25</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136">
         <v>19</v>
       </c>
       <c r="G136">
@@ -4507,7 +4582,7 @@
       <c r="E137" t="s">
         <v>26</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137">
         <v>21</v>
       </c>
       <c r="G137">
@@ -4536,7 +4611,7 @@
       <c r="E138" t="s">
         <v>27</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138">
         <v>31</v>
       </c>
       <c r="G138">
@@ -4565,7 +4640,7 @@
       <c r="E139" t="s">
         <v>28</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139">
         <v>32</v>
       </c>
       <c r="G139">
@@ -4594,7 +4669,7 @@
       <c r="E140" t="s">
         <v>29</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140">
         <v>33</v>
       </c>
       <c r="G140">
@@ -4623,7 +4698,7 @@
       <c r="E141" t="s">
         <v>30</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141">
         <v>34</v>
       </c>
       <c r="G141">
@@ -4652,7 +4727,7 @@
       <c r="E142" t="s">
         <v>31</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142">
         <v>35</v>
       </c>
       <c r="G142">
@@ -4681,7 +4756,7 @@
       <c r="E143" t="s">
         <v>32</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143">
         <v>36</v>
       </c>
       <c r="G143">
@@ -4710,7 +4785,7 @@
       <c r="E144" t="s">
         <v>33</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144">
         <v>51</v>
       </c>
       <c r="G144">
@@ -4739,7 +4814,7 @@
       <c r="E145" t="s">
         <v>34</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145">
         <v>52</v>
       </c>
       <c r="G145">
@@ -4768,7 +4843,7 @@
       <c r="E146" t="s">
         <v>35</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146">
         <v>53</v>
       </c>
       <c r="G146">
@@ -4797,7 +4872,7 @@
       <c r="E147" t="s">
         <v>36</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147">
         <v>61</v>
       </c>
       <c r="G147">
@@ -4826,7 +4901,7 @@
       <c r="E148" t="s">
         <v>37</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148">
         <v>62</v>
       </c>
       <c r="G148">
@@ -4855,7 +4930,7 @@
       <c r="E149" t="s">
         <v>38</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149">
         <v>63</v>
       </c>
       <c r="G149">
@@ -4884,7 +4959,7 @@
       <c r="E150" t="s">
         <v>39</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150">
         <v>64</v>
       </c>
       <c r="G150">
@@ -4913,7 +4988,7 @@
       <c r="E151" t="s">
         <v>40</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151">
         <v>65</v>
       </c>
       <c r="G151">
@@ -4942,7 +5017,7 @@
       <c r="E152" t="s">
         <v>41</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152">
         <v>71</v>
       </c>
       <c r="G152">
@@ -4971,7 +5046,7 @@
       <c r="E153" t="s">
         <v>42</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153">
         <v>72</v>
       </c>
       <c r="G153">
@@ -5000,7 +5075,7 @@
       <c r="E154" t="s">
         <v>43</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154">
         <v>73</v>
       </c>
       <c r="G154">
@@ -5029,7 +5104,7 @@
       <c r="E155" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="3">
+      <c r="F155">
         <v>74</v>
       </c>
       <c r="G155">
@@ -5058,7 +5133,7 @@
       <c r="E156" t="s">
         <v>45</v>
       </c>
-      <c r="F156" s="3">
+      <c r="F156">
         <v>75</v>
       </c>
       <c r="G156">
@@ -5087,7 +5162,7 @@
       <c r="E157" t="s">
         <v>46</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157">
         <v>76</v>
       </c>
       <c r="G157">
@@ -5116,7 +5191,7 @@
       <c r="E158" t="s">
         <v>47</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158">
         <v>81</v>
       </c>
       <c r="G158">
@@ -5145,7 +5220,7 @@
       <c r="E159" t="s">
         <v>48</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159">
         <v>82</v>
       </c>
       <c r="G159">
@@ -5174,7 +5249,7 @@
       <c r="E160" t="s">
         <v>49</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160">
         <v>91</v>
       </c>
       <c r="G160">
@@ -5203,7 +5278,7 @@
       <c r="E161" t="s">
         <v>50</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161">
         <v>94</v>
       </c>
       <c r="G161">
@@ -5232,7 +5307,7 @@
       <c r="E162" t="s">
         <v>51</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162">
         <v>95</v>
       </c>
       <c r="G162">
@@ -5261,7 +5336,7 @@
       <c r="E163" t="s">
         <v>52</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163">
         <v>96</v>
       </c>
       <c r="G163">
@@ -5290,7 +5365,7 @@
       <c r="E164" t="s">
         <v>53</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164">
         <v>97</v>
       </c>
       <c r="G164">
@@ -5319,7 +5394,7 @@
       <c r="E165" t="s">
         <v>54</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165">
         <v>98</v>
       </c>
       <c r="G165">
@@ -5336,4 +5411,367 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D917174-8CC3-46DB-B3DD-6F9CA7786070}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2023</v>
+      </c>
+      <c r="I2">
+        <v>272606</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2023</v>
+      </c>
+      <c r="I3">
+        <v>261197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2023</v>
+      </c>
+      <c r="I4">
+        <v>18646</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>2023</v>
+      </c>
+      <c r="I5">
+        <v>242551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2023</v>
+      </c>
+      <c r="I6">
+        <v>37451</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2023</v>
+      </c>
+      <c r="I7">
+        <v>205100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2023</v>
+      </c>
+      <c r="I8">
+        <v>27722</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>2023</v>
+      </c>
+      <c r="I9">
+        <v>177378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>2023</v>
+      </c>
+      <c r="I10">
+        <v>10339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>2023</v>
+      </c>
+      <c r="I11">
+        <v>167039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2023</v>
+      </c>
+      <c r="I12">
+        <v>55968</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>2023</v>
+      </c>
+      <c r="I13">
+        <v>111071</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>